--- a/assessment_forms/029_pre_training_skills_assessment--assessment_forms.xlsx
+++ b/assessment_forms/029_pre_training_skills_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>date_of_birth_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>date of birth</t>
+          <t>Date Of Birth 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_title_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>job title</t>
+          <t>Job Title 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>job_satisfaction</t>
+          <t>job_satisfaction_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>job satisfaction</t>
+          <t>Job Satisfaction 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>training_status</t>
+          <t>training_status_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>training status</t>
+          <t>Training Status 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2035,7 +2035,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>job_title_choices</t>
+          <t>job_title_2_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2052,7 +2052,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>job_title_choices</t>
+          <t>job_title_2_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2069,7 +2069,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>job_title_choices</t>
+          <t>job_title_2_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2086,7 +2086,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>job_title_choices</t>
+          <t>job_title_2_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2103,7 +2103,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2120,7 +2120,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2137,7 +2137,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2154,7 +2154,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>training_status_choices</t>
+          <t>training_status_2_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2171,7 +2171,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>training_status_choices</t>
+          <t>training_status_2_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2188,7 +2188,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>training_status_choices</t>
+          <t>training_status_2_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
